--- a/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
@@ -444,10 +444,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>2.1467007102959</v>
+        <v>1.54295874271649</v>
       </c>
       <c r="E2">
-        <v>10.78863650568601</v>
+        <v>19.72977856763941</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -461,10 +461,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2.0303241540224</v>
+        <v>1.435071618454</v>
       </c>
       <c r="E3">
-        <v>4.782582690670916</v>
+        <v>11.35800481852056</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -478,10 +478,10 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>1.92734148567465</v>
+        <v>1.2845040280893</v>
       </c>
       <c r="E4">
-        <v>-0.5322287104916765</v>
+        <v>-0.3256674370900944</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -495,10 +495,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1.730647378368045</v>
+        <v>1.2525365223986</v>
       </c>
       <c r="E5">
-        <v>-10.68337453752135</v>
+        <v>-2.806266737476278</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -512,10 +512,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1.91044556871566</v>
+        <v>1.26073744343646</v>
       </c>
       <c r="E6">
-        <v>-1.404206622187516</v>
+        <v>-2.169895567768284</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>2.05141854168801</v>
+        <v>1.3122419440263</v>
       </c>
       <c r="E7">
-        <v>5.871238615638286</v>
+        <v>1.826726169506179</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
@@ -444,10 +444,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1.54295874271649</v>
+        <v>1.82322707232206</v>
       </c>
       <c r="E2">
-        <v>19.72977856763941</v>
+        <v>8.50996019563719</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -461,10 +461,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.435071618454</v>
+        <v>1.907976256733</v>
       </c>
       <c r="E3">
-        <v>11.35800481852056</v>
+        <v>13.55383584154432</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -478,10 +478,10 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>1.2845040280893</v>
+        <v>1.66114407908697</v>
       </c>
       <c r="E4">
-        <v>-0.3256674370900944</v>
+        <v>-1.136462573815095</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -495,10 +495,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1.2525365223986</v>
+        <v>1.68548383583328</v>
       </c>
       <c r="E5">
-        <v>-2.806266737476278</v>
+        <v>0.3121260720028251</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -512,10 +512,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1.26073744343646</v>
+        <v>1.6789510387947</v>
       </c>
       <c r="E6">
-        <v>-2.169895567768284</v>
+        <v>-0.07667549713999845</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>1.3122419440263</v>
+        <v>1.70836195530609</v>
       </c>
       <c r="E7">
-        <v>1.826726169506179</v>
+        <v>1.673724893692071</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
@@ -444,10 +444,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1.82322707232206</v>
+        <v>1.79117962307884</v>
       </c>
       <c r="E2">
-        <v>8.50996019563719</v>
+        <v>2.514897916495243</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -461,10 +461,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.907976256733</v>
+        <v>1.931369144575585</v>
       </c>
       <c r="E3">
-        <v>13.55383584154432</v>
+        <v>10.53838941898235</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -478,10 +478,10 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>1.66114407908697</v>
+        <v>1.77402892791802</v>
       </c>
       <c r="E4">
-        <v>-1.136462573815095</v>
+        <v>1.533309168524652</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -495,10 +495,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1.68548383583328</v>
+        <v>1.714805965986315</v>
       </c>
       <c r="E5">
-        <v>0.3121260720028251</v>
+        <v>-1.856209011849364</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -512,10 +512,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1.6789510387947</v>
+        <v>1.750684231740745</v>
       </c>
       <c r="E6">
-        <v>-0.07667549713999845</v>
+        <v>0.1972180726515705</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>1.70836195530609</v>
+        <v>1.793006756094855</v>
       </c>
       <c r="E7">
-        <v>1.673724893692071</v>
+        <v>2.619470541263418</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_cmsy.xlsx
@@ -444,10 +444,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1.79117962307884</v>
+        <v>1.81501332305496</v>
       </c>
       <c r="E2">
-        <v>2.514897916495243</v>
+        <v>2.487387419449906</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -461,10 +461,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.931369144575585</v>
+        <v>1.94514744758846</v>
       </c>
       <c r="E3">
-        <v>10.53838941898235</v>
+        <v>9.835601489364967</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -478,10 +478,10 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>1.77402892791802</v>
+        <v>1.7502238718354</v>
       </c>
       <c r="E4">
-        <v>1.533309168524652</v>
+        <v>-1.17104390085371</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -495,10 +495,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1.714805965986315</v>
+        <v>1.75856096709357</v>
       </c>
       <c r="E5">
-        <v>-1.856209011849364</v>
+        <v>-0.700277598026378</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -512,10 +512,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1.750684231740745</v>
+        <v>1.754791593590925</v>
       </c>
       <c r="E6">
-        <v>0.1972180726515705</v>
+        <v>-0.9131207973501034</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>1.793006756094855</v>
+        <v>1.79806337601109</v>
       </c>
       <c r="E7">
-        <v>2.619470541263418</v>
+        <v>1.530283817311956</v>
       </c>
     </row>
   </sheetData>
